--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenni\AppData\Local\Temp\claude\C--Users-jenni-OneDrive-Desktop-DLEMBA-DNP-Fall-2026\fbf61637-3082-4084-a60e-058ce751fa06\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/119f72ca1840be2a/Desktop/DLEMBA_DNP/Fall 2026/BUS620 Economics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A44B8FF-FEAB-408A-821E-8924BEE13E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2109" documentId="13_ncr:1_{8A44B8FF-FEAB-408A-821E-8924BEE13E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E613AEE-1516-4D7E-A7E9-576B7607D559}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,51 @@
     <definedName name="MESCLUN_DIM_PCT">Inputs!$B$16</definedName>
     <definedName name="MESCLUN_FERTILIZER">Inputs!$B$15</definedName>
     <definedName name="MESCLUN_PRICE">Inputs!$B$12</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">Model!$F$2:$F$4</definedName>
+    <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">Model!$F$13</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">Model!$F$2</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">Model!$F$2:$F$4</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">Model!$F$3</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">Model!$F$4</definedName>
+    <definedName name="solver_lhs6" localSheetId="1" hidden="1">Model!$F$5</definedName>
+    <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">6</definedName>
+    <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">Model!$F$19</definedName>
+    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="1" hidden="1">4</definedName>
+    <definedName name="solver_rel4" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">4</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">20</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">24</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">34</definedName>
+    <definedName name="solver_rhs6" localSheetId="1" hidden="1">64</definedName>
+    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="TEMP_WAGE">Inputs!$B$24</definedName>
     <definedName name="TEMP_WORKER_HOURLY_RATE">Inputs!$B$26</definedName>
     <definedName name="TEMP_WORKER_HOURS">Inputs!$B$25</definedName>
@@ -452,7 +497,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,11 +512,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -494,16 +551,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -1319,16 +1379,16 @@
         <v>59</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
@@ -1336,16 +1396,16 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
@@ -1353,16 +1413,16 @@
         <v>61</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
@@ -1371,19 +1431,19 @@
       </c>
       <c r="C5">
         <f>SUM(C2:C4)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <f>SUM(D2:D4)</f>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E5">
         <f>SUM(E2:E4)</f>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F5">
         <f>SUM(F2:F4)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
@@ -1392,19 +1452,19 @@
       </c>
       <c r="C7">
         <f>C2*TOMATO_BASE_LABOR*WEEKS*(1+TOMATO_DIM_PCT)^C2</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
       <c r="D7">
         <f>D2*TOMATO_BASE_LABOR*WEEKS*(1+TOMATO_DIM_PCT)^D2</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
       <c r="E7">
         <f>E2*TOMATO_BASE_LABOR*WEEKS*(1+TOMATO_DIM_PCT)^E2</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
       <c r="F7">
         <f>F2*TOMATO_BASE_LABOR*WEEKS*(1+TOMATO_DIM_PCT)^F2</f>
-        <v>0</v>
+        <v>2334.3682140900019</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
@@ -1413,19 +1473,19 @@
       </c>
       <c r="C8">
         <f>C3*CARROT_BASE_LABOR*WEEKS*(1+CARROT_DIM_PCT)^C3</f>
-        <v>0</v>
+        <v>983.16986417423732</v>
       </c>
       <c r="D8">
         <f>D3*CARROT_BASE_LABOR*WEEKS*(1+CARROT_DIM_PCT)^D3</f>
-        <v>0</v>
+        <v>1058.1365663175229</v>
       </c>
       <c r="E8">
         <f>E3*CARROT_BASE_LABOR*WEEKS*(1+CARROT_DIM_PCT)^E3</f>
-        <v>0</v>
+        <v>983.16986417423732</v>
       </c>
       <c r="F8">
         <f>F3*CARROT_BASE_LABOR*WEEKS*(1+CARROT_DIM_PCT)^F3</f>
-        <v>0</v>
+        <v>1217.5813709385234</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
@@ -1434,19 +1494,19 @@
       </c>
       <c r="C9">
         <f>C4*MESCLUN_BASE_LABOR*WEEKS*(1+MESCLUN_DIM_PCT)^C4</f>
-        <v>0</v>
+        <v>1959.6780360096488</v>
       </c>
       <c r="D9">
         <f>D4*MESCLUN_BASE_LABOR*WEEKS*(1+MESCLUN_DIM_PCT)^D4</f>
-        <v>0</v>
+        <v>1959.6780360096488</v>
       </c>
       <c r="E9">
         <f>E4*MESCLUN_BASE_LABOR*WEEKS*(1+MESCLUN_DIM_PCT)^E4</f>
-        <v>0</v>
+        <v>2050.3131451750946</v>
       </c>
       <c r="F9">
         <f>F4*MESCLUN_BASE_LABOR*WEEKS*(1+MESCLUN_DIM_PCT)^F4</f>
-        <v>0</v>
+        <v>2050.3131451750946</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
@@ -1455,19 +1515,19 @@
       </c>
       <c r="C10">
         <f>SUM(C7:C9)</f>
-        <v>0</v>
+        <v>5277.2161142738878</v>
       </c>
       <c r="D10">
         <f>SUM(D7:D9)</f>
-        <v>0</v>
+        <v>5352.1828164171739</v>
       </c>
       <c r="E10">
         <f>SUM(E7:E9)</f>
-        <v>0</v>
+        <v>5367.8512234393338</v>
       </c>
       <c r="F10">
         <f>SUM(F7:F9)</f>
-        <v>0</v>
+        <v>5602.2627302036199</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
@@ -1476,19 +1536,19 @@
       </c>
       <c r="C11">
         <f>MIN(C10,FARMER_HOURS)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="D11">
         <f>MIN(D10,FARMER_HOURS)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E11">
         <f>MIN(E10,FARMER_HOURS)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="F11">
         <f>MIN(F10,FARMER_HOURS)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
@@ -1497,19 +1557,19 @@
       </c>
       <c r="C12">
         <f>MAX(0,C10-FARMER_HOURS)</f>
-        <v>0</v>
+        <v>4557.2161142738878</v>
       </c>
       <c r="D12">
         <f>MAX(0,D10-FARMER_HOURS)</f>
-        <v>0</v>
+        <v>4632.1828164171739</v>
       </c>
       <c r="E12">
         <f>MAX(0,E10-FARMER_HOURS)</f>
-        <v>0</v>
+        <v>4647.8512234393338</v>
       </c>
       <c r="F12">
         <f>MAX(0,F10-FARMER_HOURS)</f>
-        <v>0</v>
+        <v>4882.2627302036199</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
@@ -1518,19 +1578,19 @@
       </c>
       <c r="C13">
         <f>IF(C12=0,0,ROUNDUP(C12/TEMP_WORKER_HOURS,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <f>IF(D12=0,0,ROUNDUP(D12/TEMP_WORKER_HOURS,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <f>IF(E12=0,0,ROUNDUP(E12/TEMP_WORKER_HOURS,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <f>IF(F12=0,0,ROUNDUP(F12/TEMP_WORKER_HOURS,0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
@@ -1539,19 +1599,19 @@
       </c>
       <c r="C14">
         <f>C11*FARMER_HOURLY_RATE+C12*TEMP_WORKER_HOURLY_RATE</f>
-        <v>0</v>
+        <v>104118.335317255</v>
       </c>
       <c r="D14">
         <f>D11*FARMER_HOURLY_RATE+D12*TEMP_WORKER_HOURLY_RATE</f>
-        <v>0</v>
+        <v>105419.84056279816</v>
       </c>
       <c r="E14">
         <f>E11*FARMER_HOURLY_RATE+E12*TEMP_WORKER_HOURLY_RATE</f>
-        <v>0</v>
+        <v>105691.86151804398</v>
       </c>
       <c r="F14">
         <f>F11*FARMER_HOURLY_RATE+F12*TEMP_WORKER_HOURLY_RATE</f>
-        <v>0</v>
+        <v>109761.50573270173</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
@@ -1560,19 +1620,19 @@
       </c>
       <c r="C15">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v>0</v>
+        <v>19.729784239010844</v>
       </c>
       <c r="D15">
         <f>IF(D10=0,0,D14/D10)</f>
-        <v>0</v>
+        <v>19.696606819826023</v>
       </c>
       <c r="E15">
         <f>IF(E10=0,0,E14/E10)</f>
-        <v>0</v>
+        <v>19.689789660437761</v>
       </c>
       <c r="F15">
         <f>IF(F10=0,0,F14/F10)</f>
-        <v>0</v>
+        <v>19.592352415202122</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
@@ -1581,19 +1641,19 @@
       </c>
       <c r="C17">
         <f>C2*TOMATO_FERTILIZER+C3*CARROT_FERTILIZER+C4*MESCLUN_FERTILIZER</f>
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="D17">
         <f>D2*TOMATO_FERTILIZER+D3*CARROT_FERTILIZER+D4*MESCLUN_FERTILIZER</f>
-        <v>0</v>
+        <v>44440</v>
       </c>
       <c r="E17">
         <f>E2*TOMATO_FERTILIZER+E3*CARROT_FERTILIZER+E4*MESCLUN_FERTILIZER</f>
-        <v>0</v>
+        <v>44880</v>
       </c>
       <c r="F17">
         <f>F2*TOMATO_FERTILIZER+F3*CARROT_FERTILIZER+F4*MESCLUN_FERTILIZER</f>
-        <v>0</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
@@ -1602,40 +1662,40 @@
       </c>
       <c r="C18">
         <f>C2*TOMATO_PRICE+C3*CARROT_PRICE+C4*MESCLUN_PRICE</f>
-        <v>0</v>
+        <v>210880</v>
       </c>
       <c r="D18">
         <f>D2*TOMATO_PRICE+D3*CARROT_PRICE+D4*MESCLUN_PRICE</f>
-        <v>0</v>
+        <v>212974</v>
       </c>
       <c r="E18">
         <f>E2*TOMATO_PRICE+E3*CARROT_PRICE+E4*MESCLUN_PRICE</f>
-        <v>0</v>
+        <v>213580</v>
       </c>
       <c r="F18">
         <f>F2*TOMATO_PRICE+F3*CARROT_PRICE+F4*MESCLUN_PRICE</f>
-        <v>0</v>
+        <v>219862</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>74</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4">
         <f>C18-C17-C14-FIXED_COSTS</f>
-        <v>-20000</v>
-      </c>
-      <c r="D19">
+        <v>42761.664682745002</v>
+      </c>
+      <c r="D19" s="4">
         <f>D18-D17-D14-FIXED_COSTS</f>
-        <v>-20000</v>
-      </c>
-      <c r="E19">
+        <v>43114.159437201844</v>
+      </c>
+      <c r="E19" s="4">
         <f>E18-E17-E14-FIXED_COSTS</f>
-        <v>-20000</v>
-      </c>
-      <c r="F19">
+        <v>43008.138481956019</v>
+      </c>
+      <c r="F19" s="4">
         <f>F18-F17-F14-FIXED_COSTS</f>
-        <v>-20000</v>
+        <v>43900.494267298272</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
@@ -1855,7 +1915,7 @@
       </c>
       <c r="B10">
         <f>Model!C2</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1865,7 +1925,7 @@
       </c>
       <c r="E10" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -1874,7 +1934,7 @@
       </c>
       <c r="B11">
         <f>Model!C3</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>20</v>
@@ -1884,7 +1944,7 @@
       </c>
       <c r="E11" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -1893,7 +1953,7 @@
       </c>
       <c r="B12">
         <f>Model!C4</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>30</v>
@@ -1903,7 +1963,7 @@
       </c>
       <c r="E12" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -1912,7 +1972,7 @@
       </c>
       <c r="B13">
         <f>Model!C19</f>
-        <v>-20000</v>
+        <v>42761.664682745002</v>
       </c>
       <c r="C13">
         <v>42762</v>
@@ -1922,7 +1982,7 @@
       </c>
       <c r="E13" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -1950,7 +2010,7 @@
       </c>
       <c r="B15">
         <f>Model!D19-Model!C19</f>
-        <v>0</v>
+        <v>352.4947544568422</v>
       </c>
       <c r="C15">
         <v>352</v>
@@ -1960,7 +2020,7 @@
       </c>
       <c r="E15" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -1969,7 +2029,7 @@
       </c>
       <c r="B16">
         <f>Model!E19-Model!C19</f>
-        <v>0</v>
+        <v>246.47379921101674</v>
       </c>
       <c r="C16">
         <v>246</v>
@@ -1979,7 +2039,7 @@
       </c>
       <c r="E16" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -1988,7 +2048,7 @@
       </c>
       <c r="B17">
         <f>Model!C12</f>
-        <v>0</v>
+        <v>4557.2161142738878</v>
       </c>
       <c r="C17">
         <v>5760</v>
@@ -2048,7 +2108,7 @@
       </c>
       <c r="C2">
         <f>Model!C2</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>104</v>
@@ -2063,7 +2123,7 @@
       </c>
       <c r="C3">
         <f>Model!C3</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
@@ -2078,7 +2138,7 @@
       </c>
       <c r="C4">
         <f>Model!C4</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>108</v>
@@ -2093,7 +2153,7 @@
       </c>
       <c r="C5">
         <f>Model!C5</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>110</v>
@@ -2108,7 +2168,7 @@
       </c>
       <c r="C6">
         <f>Model!C10</f>
-        <v>0</v>
+        <v>5277.2161142738878</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -2123,7 +2183,7 @@
       </c>
       <c r="C7">
         <f>Model!C15</f>
-        <v>0</v>
+        <v>19.729784239010844</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -2138,7 +2198,7 @@
       </c>
       <c r="C8">
         <f>Model!C19</f>
-        <v>-20000</v>
+        <v>42761.664682745002</v>
       </c>
       <c r="D8" t="s">
         <v>117</v>
@@ -2168,7 +2228,7 @@
       </c>
       <c r="C10">
         <f>Model!D19-Model!C19</f>
-        <v>0</v>
+        <v>352.4947544568422</v>
       </c>
       <c r="D10" t="s">
         <v>120</v>
@@ -2183,7 +2243,7 @@
       </c>
       <c r="C11">
         <f>Model!E19-Model!C19</f>
-        <v>0</v>
+        <v>246.47379921101674</v>
       </c>
       <c r="D11" t="s">
         <v>121</v>
@@ -2198,7 +2258,7 @@
       </c>
       <c r="C12">
         <f>Model!F19</f>
-        <v>-20000</v>
+        <v>43900.494267298272</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
@@ -2213,7 +2273,7 @@
       </c>
       <c r="C13">
         <f>Model!F19-Model!C19</f>
-        <v>0</v>
+        <v>1138.8295845532703</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
